--- a/docs/Items.xlsx
+++ b/docs/Items.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\RE_Modding\BioRand\re7\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D2C89D0-B792-4CAB-A9B1-439430F4E8C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC687770-2D01-44DC-A64D-2A7242C2C943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{DE583D23-C62C-4A13-9B57-9882812AC707}"/>
+    <workbookView xWindow="38280" yWindow="2220" windowWidth="29040" windowHeight="15720" xr2:uid="{DE583D23-C62C-4A13-9B57-9882812AC707}"/>
   </bookViews>
   <sheets>
     <sheet name="items" sheetId="2" r:id="rId1"/>
@@ -2507,18 +2507,7 @@
   </cellStyles>
   <dxfs count="13">
     <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <extLst>
@@ -2545,13 +2534,24 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -2625,22 +2625,35 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8997F09E-7585-4546-A99D-93C95A83DDE6}" name="items" displayName="items" ref="A1:N314" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:N314" xr:uid="{8997F09E-7585-4546-A99D-93C95A83DDE6}"/>
+  <autoFilter ref="A1:N314" xr:uid="{8997F09E-7585-4546-A99D-93C95A83DDE6}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Drug"/>
+        <filter val="Material"/>
+        <filter val="Shell"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="13">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{F0F4938D-6AE6-4FD1-903A-6D70073C8CFE}" uniqueName="1" name="Id" queryTableFieldId="1" dataDxfId="12"/>
     <tableColumn id="2" xr3:uid="{0EDD0777-3DC7-4A87-90CA-8CAF0D26BB97}" uniqueName="2" name="Name" queryTableFieldId="2" dataDxfId="11"/>
     <tableColumn id="3" xr3:uid="{B6646755-3DE3-4BD1-9736-C1C0F0FF8BF4}" uniqueName="3" name="CategoryType" queryTableFieldId="3" dataDxfId="10"/>
     <tableColumn id="4" xr3:uid="{693AC4C5-7997-4B21-8AA9-7D80E998DAD2}" uniqueName="4" name="Size" queryTableFieldId="4" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{03B245DF-8ED8-4B68-9F1F-687820CA55CF}" uniqueName="5" name="IsUnlockable" queryTableFieldId="5" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{C1461D35-E3E1-434D-A82B-EBF6CE36D7CB}" uniqueName="6" name="Dlc" queryTableFieldId="6" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{03B245DF-8ED8-4B68-9F1F-687820CA55CF}" uniqueName="5" name="IsUnlockable" queryTableFieldId="5" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{C1461D35-E3E1-434D-A82B-EBF6CE36D7CB}" uniqueName="6" name="Dlc" queryTableFieldId="6" dataDxfId="7"/>
     <tableColumn id="7" xr3:uid="{2BB988DD-AE22-4430-814E-0B7839B7862E}" uniqueName="7" name="MaxStack" queryTableFieldId="7"/>
-    <tableColumn id="8" xr3:uid="{24289E5C-199D-4D7D-A529-03FEF8D684FB}" uniqueName="8" name="WeaponId" queryTableFieldId="8" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{E369F7E8-1F03-4F52-A9A6-5E43A328E7C0}" uniqueName="9" name="CanStoreInItemBox" queryTableFieldId="9" dataDxfId="4"/>
-    <tableColumn id="10" xr3:uid="{732DA774-613C-4E2F-A377-F55D682D67CD}" uniqueName="10" name="DeveloperComment" queryTableFieldId="10" dataDxfId="6"/>
-    <tableColumn id="11" xr3:uid="{09330990-6228-4142-9F3F-94CEC1B7C15E}" uniqueName="11" name="IsWeapon" queryTableFieldId="11" dataDxfId="2"/>
-    <tableColumn id="12" xr3:uid="{EF857BE0-497D-4F7C-82C8-0EF4A81199B7}" uniqueName="12" name="IsStackable" queryTableFieldId="12" dataDxfId="1"/>
-    <tableColumn id="13" xr3:uid="{DD0473B1-B283-4D27-AC46-793161B504DD}" uniqueName="13" name="IsDlcItem" queryTableFieldId="13" dataDxfId="0"/>
-    <tableColumn id="14" xr3:uid="{87E2BCDC-6BFE-4E47-A00B-A01A9868C43C}" uniqueName="14" name="ItemId" queryTableFieldId="14" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{24289E5C-199D-4D7D-A529-03FEF8D684FB}" uniqueName="8" name="WeaponId" queryTableFieldId="8" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{E369F7E8-1F03-4F52-A9A6-5E43A328E7C0}" uniqueName="9" name="CanStoreInItemBox" queryTableFieldId="9" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{732DA774-613C-4E2F-A377-F55D682D67CD}" uniqueName="10" name="DeveloperComment" queryTableFieldId="10" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{09330990-6228-4142-9F3F-94CEC1B7C15E}" uniqueName="11" name="IsWeapon" queryTableFieldId="11" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{EF857BE0-497D-4F7C-82C8-0EF4A81199B7}" uniqueName="12" name="IsStackable" queryTableFieldId="12" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{DD0473B1-B283-4D27-AC46-793161B504DD}" uniqueName="13" name="IsDlcItem" queryTableFieldId="13" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{87E2BCDC-6BFE-4E47-A00B-A01A9868C43C}" uniqueName="14" name="ItemId" queryTableFieldId="14" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3026,7 +3039,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -3070,7 +3083,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -3114,7 +3127,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -3158,7 +3171,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -3246,7 +3259,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -3290,7 +3303,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>37</v>
       </c>
@@ -3334,7 +3347,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -3378,7 +3391,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -3422,7 +3435,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>46</v>
       </c>
@@ -3466,7 +3479,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>48</v>
       </c>
@@ -3510,7 +3523,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>51</v>
       </c>
@@ -3554,7 +3567,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>54</v>
       </c>
@@ -3598,7 +3611,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>55</v>
       </c>
@@ -3642,7 +3655,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>60</v>
       </c>
@@ -3686,7 +3699,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>63</v>
       </c>
@@ -3730,7 +3743,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>66</v>
       </c>
@@ -3774,7 +3787,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>69</v>
       </c>
@@ -3818,7 +3831,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>72</v>
       </c>
@@ -3862,7 +3875,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>74</v>
       </c>
@@ -3906,7 +3919,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>77</v>
       </c>
@@ -3950,7 +3963,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>80</v>
       </c>
@@ -3994,7 +4007,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>83</v>
       </c>
@@ -4038,7 +4051,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>86</v>
       </c>
@@ -4082,7 +4095,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>89</v>
       </c>
@@ -4126,7 +4139,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>91</v>
       </c>
@@ -4170,7 +4183,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>94</v>
       </c>
@@ -4258,7 +4271,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>97</v>
       </c>
@@ -4302,7 +4315,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>99</v>
       </c>
@@ -4346,7 +4359,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>101</v>
       </c>
@@ -4390,7 +4403,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>104</v>
       </c>
@@ -4434,7 +4447,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>105</v>
       </c>
@@ -4478,7 +4491,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>106</v>
       </c>
@@ -4522,7 +4535,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>109</v>
       </c>
@@ -4566,7 +4579,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>111</v>
       </c>
@@ -4610,7 +4623,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>113</v>
       </c>
@@ -4654,7 +4667,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>115</v>
       </c>
@@ -4698,7 +4711,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>118</v>
       </c>
@@ -4742,7 +4755,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>121</v>
       </c>
@@ -4786,7 +4799,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>123</v>
       </c>
@@ -4830,7 +4843,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>125</v>
       </c>
@@ -4874,7 +4887,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>128</v>
       </c>
@@ -4918,7 +4931,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>131</v>
       </c>
@@ -5094,7 +5107,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>143</v>
       </c>
@@ -5138,7 +5151,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>145</v>
       </c>
@@ -5182,7 +5195,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>146</v>
       </c>
@@ -5226,7 +5239,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>149</v>
       </c>
@@ -5270,7 +5283,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>152</v>
       </c>
@@ -5314,7 +5327,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>155</v>
       </c>
@@ -5358,7 +5371,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>159</v>
       </c>
@@ -5402,7 +5415,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>162</v>
       </c>
@@ -5446,7 +5459,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>165</v>
       </c>
@@ -5490,7 +5503,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>167</v>
       </c>
@@ -5534,7 +5547,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>169</v>
       </c>
@@ -5578,7 +5591,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>171</v>
       </c>
@@ -5666,7 +5679,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>177</v>
       </c>
@@ -5710,7 +5723,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>179</v>
       </c>
@@ -5754,7 +5767,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>182</v>
       </c>
@@ -5798,7 +5811,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>184</v>
       </c>
@@ -5842,7 +5855,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>186</v>
       </c>
@@ -5886,7 +5899,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>189</v>
       </c>
@@ -5930,7 +5943,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>192</v>
       </c>
@@ -5974,7 +5987,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>194</v>
       </c>
@@ -6018,7 +6031,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>196</v>
       </c>
@@ -6062,7 +6075,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>200</v>
       </c>
@@ -6106,7 +6119,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>203</v>
       </c>
@@ -6150,7 +6163,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>206</v>
       </c>
@@ -6194,7 +6207,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>209</v>
       </c>
@@ -6238,7 +6251,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>212</v>
       </c>
@@ -6282,7 +6295,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>215</v>
       </c>
@@ -6326,7 +6339,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>218</v>
       </c>
@@ -6370,7 +6383,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>221</v>
       </c>
@@ -6414,7 +6427,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>224</v>
       </c>
@@ -6458,7 +6471,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>227</v>
       </c>
@@ -6502,7 +6515,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>230</v>
       </c>
@@ -6546,7 +6559,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>233</v>
       </c>
@@ -6590,7 +6603,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>236</v>
       </c>
@@ -6634,7 +6647,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>239</v>
       </c>
@@ -6678,7 +6691,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>242</v>
       </c>
@@ -6722,7 +6735,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>245</v>
       </c>
@@ -6766,7 +6779,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>248</v>
       </c>
@@ -6810,7 +6823,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>250</v>
       </c>
@@ -6854,7 +6867,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>252</v>
       </c>
@@ -6898,7 +6911,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>254</v>
       </c>
@@ -6942,7 +6955,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>257</v>
       </c>
@@ -6986,7 +6999,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>260</v>
       </c>
@@ -7030,7 +7043,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>262</v>
       </c>
@@ -7074,7 +7087,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>265</v>
       </c>
@@ -7118,7 +7131,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>267</v>
       </c>
@@ -7162,7 +7175,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>269</v>
       </c>
@@ -7206,7 +7219,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>271</v>
       </c>
@@ -7250,7 +7263,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>274</v>
       </c>
@@ -7382,7 +7395,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>281</v>
       </c>
@@ -7426,7 +7439,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>284</v>
       </c>
@@ -7470,7 +7483,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>287</v>
       </c>
@@ -7514,7 +7527,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>290</v>
       </c>
@@ -7558,7 +7571,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>293</v>
       </c>
@@ -7602,7 +7615,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>296</v>
       </c>
@@ -7646,7 +7659,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>299</v>
       </c>
@@ -7690,7 +7703,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>302</v>
       </c>
@@ -7734,7 +7747,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>305</v>
       </c>
@@ -7778,7 +7791,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>308</v>
       </c>
@@ -7822,7 +7835,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>311</v>
       </c>
@@ -7866,7 +7879,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>314</v>
       </c>
@@ -7910,7 +7923,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>317</v>
       </c>
@@ -7954,7 +7967,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>320</v>
       </c>
@@ -7998,7 +8011,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>323</v>
       </c>
@@ -8042,7 +8055,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>326</v>
       </c>
@@ -8086,7 +8099,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>329</v>
       </c>
@@ -8130,7 +8143,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>332</v>
       </c>
@@ -8174,7 +8187,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>335</v>
       </c>
@@ -8218,7 +8231,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>338</v>
       </c>
@@ -8262,7 +8275,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>341</v>
       </c>
@@ -8306,7 +8319,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>344</v>
       </c>
@@ -8350,7 +8363,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>346</v>
       </c>
@@ -8394,7 +8407,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>348</v>
       </c>
@@ -8438,7 +8451,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>350</v>
       </c>
@@ -8482,7 +8495,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>353</v>
       </c>
@@ -8526,7 +8539,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>354</v>
       </c>
@@ -8570,7 +8583,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>357</v>
       </c>
@@ -8614,7 +8627,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>360</v>
       </c>
@@ -8658,7 +8671,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>363</v>
       </c>
@@ -8702,7 +8715,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>365</v>
       </c>
@@ -8746,7 +8759,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>367</v>
       </c>
@@ -8790,7 +8803,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>370</v>
       </c>
@@ -8834,7 +8847,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>373</v>
       </c>
@@ -8878,7 +8891,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>376</v>
       </c>
@@ -8922,7 +8935,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>379</v>
       </c>
@@ -8966,7 +8979,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>382</v>
       </c>
@@ -9010,7 +9023,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>385</v>
       </c>
@@ -9054,7 +9067,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>388</v>
       </c>
@@ -9098,7 +9111,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>391</v>
       </c>
@@ -9142,7 +9155,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>392</v>
       </c>
@@ -9186,7 +9199,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>395</v>
       </c>
@@ -9230,7 +9243,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>398</v>
       </c>
@@ -9274,7 +9287,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>401</v>
       </c>
@@ -9318,7 +9331,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>403</v>
       </c>
@@ -9362,7 +9375,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>404</v>
       </c>
@@ -9406,7 +9419,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>408</v>
       </c>
@@ -9450,7 +9463,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>412</v>
       </c>
@@ -9494,7 +9507,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>416</v>
       </c>
@@ -9538,7 +9551,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>420</v>
       </c>
@@ -9582,7 +9595,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>424</v>
       </c>
@@ -9626,7 +9639,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>427</v>
       </c>
@@ -9714,7 +9727,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>431</v>
       </c>
@@ -9758,7 +9771,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>433</v>
       </c>
@@ -9802,7 +9815,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>435</v>
       </c>
@@ -9846,7 +9859,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>437</v>
       </c>
@@ -9890,7 +9903,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>439</v>
       </c>
@@ -9934,7 +9947,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>441</v>
       </c>
@@ -9978,7 +9991,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>443</v>
       </c>
@@ -10110,7 +10123,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>449</v>
       </c>
@@ -10198,7 +10211,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>453</v>
       </c>
@@ -10242,7 +10255,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>455</v>
       </c>
@@ -10286,7 +10299,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>456</v>
       </c>
@@ -10330,7 +10343,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>366</v>
       </c>
@@ -10374,7 +10387,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>459</v>
       </c>
@@ -10418,7 +10431,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>461</v>
       </c>
@@ -10462,7 +10475,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>462</v>
       </c>
@@ -10506,7 +10519,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>465</v>
       </c>
@@ -10550,7 +10563,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>468</v>
       </c>
@@ -10594,7 +10607,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>471</v>
       </c>
@@ -10638,7 +10651,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>472</v>
       </c>
@@ -10682,7 +10695,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>474</v>
       </c>
@@ -10726,7 +10739,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>477</v>
       </c>
@@ -10770,7 +10783,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>480</v>
       </c>
@@ -10814,7 +10827,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>483</v>
       </c>
@@ -10902,7 +10915,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>487</v>
       </c>
@@ -10946,7 +10959,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>490</v>
       </c>
@@ -11034,7 +11047,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>494</v>
       </c>
@@ -11078,7 +11091,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>117</v>
       </c>
@@ -11122,7 +11135,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>498</v>
       </c>
@@ -11166,7 +11179,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>501</v>
       </c>
@@ -11210,7 +11223,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>503</v>
       </c>
@@ -11254,7 +11267,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>505</v>
       </c>
@@ -11298,7 +11311,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>507</v>
       </c>
@@ -11342,7 +11355,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>510</v>
       </c>
@@ -11386,7 +11399,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>513</v>
       </c>
@@ -11430,7 +11443,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>515</v>
       </c>
@@ -11474,7 +11487,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>517</v>
       </c>
@@ -11518,7 +11531,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>520</v>
       </c>
@@ -11562,7 +11575,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>523</v>
       </c>
@@ -11606,7 +11619,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>526</v>
       </c>
@@ -11650,7 +11663,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>529</v>
       </c>
@@ -11694,7 +11707,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>532</v>
       </c>
@@ -11738,7 +11751,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>535</v>
       </c>
@@ -11782,7 +11795,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>538</v>
       </c>
@@ -11826,7 +11839,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>541</v>
       </c>
@@ -11870,7 +11883,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>544</v>
       </c>
@@ -11914,7 +11927,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>547</v>
       </c>
@@ -11958,7 +11971,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>549</v>
       </c>
@@ -12002,7 +12015,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>551</v>
       </c>
@@ -12134,7 +12147,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>557</v>
       </c>
@@ -12178,7 +12191,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>559</v>
       </c>
@@ -12222,7 +12235,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>562</v>
       </c>
@@ -12266,7 +12279,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>565</v>
       </c>
@@ -12310,7 +12323,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>567</v>
       </c>
@@ -12354,7 +12367,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>569</v>
       </c>
@@ -12398,7 +12411,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>572</v>
       </c>
@@ -12442,7 +12455,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>575</v>
       </c>
@@ -12486,7 +12499,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>577</v>
       </c>
@@ -12530,7 +12543,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>579</v>
       </c>
@@ -12574,7 +12587,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>581</v>
       </c>
@@ -12618,7 +12631,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>583</v>
       </c>
@@ -12662,7 +12675,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>586</v>
       </c>
@@ -12706,7 +12719,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>589</v>
       </c>
@@ -12750,7 +12763,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>592</v>
       </c>
@@ -12794,7 +12807,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>595</v>
       </c>
@@ -12838,7 +12851,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>597</v>
       </c>
@@ -12926,7 +12939,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>601</v>
       </c>
@@ -12970,7 +12983,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>603</v>
       </c>
@@ -13014,7 +13027,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>606</v>
       </c>
@@ -13058,7 +13071,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>609</v>
       </c>
@@ -13102,7 +13115,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>611</v>
       </c>
@@ -13146,7 +13159,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>614</v>
       </c>
@@ -13190,7 +13203,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>615</v>
       </c>
@@ -13234,7 +13247,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>618</v>
       </c>
@@ -13278,7 +13291,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>619</v>
       </c>
@@ -13322,7 +13335,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>622</v>
       </c>
@@ -13366,7 +13379,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>623</v>
       </c>
@@ -13410,7 +13423,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>626</v>
       </c>
@@ -13454,7 +13467,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>627</v>
       </c>
@@ -13498,7 +13511,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>630</v>
       </c>
@@ -13542,7 +13555,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>631</v>
       </c>
@@ -13586,7 +13599,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>634</v>
       </c>
@@ -13630,7 +13643,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>635</v>
       </c>
@@ -13674,7 +13687,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>638</v>
       </c>
@@ -13718,7 +13731,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>639</v>
       </c>
@@ -13762,7 +13775,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>642</v>
       </c>
@@ -13806,7 +13819,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>643</v>
       </c>
@@ -13850,7 +13863,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>646</v>
       </c>
@@ -13894,7 +13907,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>647</v>
       </c>
@@ -13938,7 +13951,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>650</v>
       </c>
@@ -13982,7 +13995,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>651</v>
       </c>
@@ -14026,7 +14039,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>654</v>
       </c>
@@ -14070,7 +14083,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>655</v>
       </c>
@@ -14114,7 +14127,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>658</v>
       </c>
@@ -14158,7 +14171,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>659</v>
       </c>
@@ -14202,7 +14215,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>662</v>
       </c>
@@ -14246,7 +14259,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>663</v>
       </c>
@@ -14290,7 +14303,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>666</v>
       </c>
@@ -14334,7 +14347,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>667</v>
       </c>
@@ -14378,7 +14391,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>670</v>
       </c>
@@ -14422,7 +14435,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>671</v>
       </c>
@@ -14466,7 +14479,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>674</v>
       </c>
@@ -14510,7 +14523,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>675</v>
       </c>
@@ -14554,7 +14567,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>678</v>
       </c>
@@ -14598,7 +14611,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>679</v>
       </c>
@@ -14642,7 +14655,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>682</v>
       </c>
@@ -14686,7 +14699,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>683</v>
       </c>
@@ -14730,7 +14743,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>686</v>
       </c>
@@ -14774,7 +14787,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>687</v>
       </c>
@@ -14818,7 +14831,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>690</v>
       </c>
@@ -14862,7 +14875,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>691</v>
       </c>
@@ -14906,7 +14919,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>694</v>
       </c>
@@ -14950,7 +14963,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>695</v>
       </c>
@@ -14994,7 +15007,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>698</v>
       </c>
@@ -15038,7 +15051,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>699</v>
       </c>
@@ -15082,7 +15095,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>702</v>
       </c>
@@ -15126,7 +15139,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>703</v>
       </c>
@@ -15170,7 +15183,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>705</v>
       </c>
@@ -15214,7 +15227,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>707</v>
       </c>
@@ -15258,7 +15271,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>710</v>
       </c>
@@ -15302,7 +15315,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>713</v>
       </c>
@@ -15346,7 +15359,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>715</v>
       </c>
@@ -15390,7 +15403,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>717</v>
       </c>
@@ -15434,7 +15447,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>720</v>
       </c>
@@ -15478,7 +15491,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>723</v>
       </c>
@@ -15522,7 +15535,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>726</v>
       </c>
@@ -15566,7 +15579,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>729</v>
       </c>
@@ -15610,7 +15623,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>732</v>
       </c>
@@ -15654,7 +15667,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>735</v>
       </c>
@@ -15698,7 +15711,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>738</v>
       </c>
@@ -15742,7 +15755,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>741</v>
       </c>
@@ -15786,7 +15799,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>744</v>
       </c>
@@ -15830,7 +15843,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>746</v>
       </c>
@@ -15874,7 +15887,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>749</v>
       </c>
@@ -15962,7 +15975,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>754</v>
       </c>
@@ -16006,7 +16019,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>757</v>
       </c>
@@ -16050,7 +16063,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>759</v>
       </c>
@@ -16094,7 +16107,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>762</v>
       </c>
@@ -16138,7 +16151,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>764</v>
       </c>
@@ -16182,7 +16195,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>766</v>
       </c>
@@ -16226,7 +16239,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>769</v>
       </c>
@@ -16270,7 +16283,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>772</v>
       </c>
@@ -16314,7 +16327,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>775</v>
       </c>
@@ -16358,7 +16371,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>778</v>
       </c>
@@ -16402,7 +16415,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>781</v>
       </c>
@@ -16446,7 +16459,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>784</v>
       </c>
@@ -16490,7 +16503,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>787</v>
       </c>
@@ -16534,7 +16547,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>790</v>
       </c>
@@ -16578,7 +16591,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>792</v>
       </c>
@@ -16622,7 +16635,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>794</v>
       </c>
@@ -16666,7 +16679,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>797</v>
       </c>
@@ -16710,7 +16723,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>799</v>
       </c>
@@ -16754,7 +16767,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>801</v>
       </c>

--- a/docs/Items.xlsx
+++ b/docs/Items.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\RE_Modding\BioRand\re7\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC687770-2D01-44DC-A64D-2A7242C2C943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72A360A7-BD33-4A23-9CD3-3A847A46CEC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="2220" windowWidth="29040" windowHeight="15720" xr2:uid="{DE583D23-C62C-4A13-9B57-9882812AC707}"/>
+    <workbookView xWindow="38400" yWindow="2580" windowWidth="28800" windowHeight="15345" xr2:uid="{DE583D23-C62C-4A13-9B57-9882812AC707}"/>
   </bookViews>
   <sheets>
     <sheet name="items" sheetId="2" r:id="rId1"/>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="ExterneDaten_1" localSheetId="0" hidden="1">items!$A$1:$N$314</definedName>
@@ -2626,17 +2625,18 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8997F09E-7585-4546-A99D-93C95A83DDE6}" name="items" displayName="items" ref="A1:N314" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:N314" xr:uid="{8997F09E-7585-4546-A99D-93C95A83DDE6}">
-    <filterColumn colId="2">
+    <filterColumn colId="3">
       <filters>
-        <filter val="Drug"/>
-        <filter val="Material"/>
-        <filter val="Shell"/>
+        <filter val="Slot1"/>
       </filters>
     </filterColumn>
-    <filterColumn colId="13">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
+    <filterColumn colId="4">
+      <filters>
+        <filter val="WAHR"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="5">
+      <filters blank="1"/>
     </filterColumn>
   </autoFilter>
   <tableColumns count="14">
@@ -3215,7 +3215,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -3391,7 +3391,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -4007,7 +4007,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="24" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>83</v>
       </c>
@@ -4051,7 +4051,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>86</v>
       </c>
@@ -4227,7 +4227,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>95</v>
       </c>
@@ -4975,7 +4975,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>134</v>
       </c>
@@ -5019,7 +5019,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>137</v>
       </c>
@@ -5063,7 +5063,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>140</v>
       </c>
@@ -5107,7 +5107,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="49" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>143</v>
       </c>
@@ -5371,7 +5371,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>159</v>
       </c>
@@ -5635,7 +5635,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>174</v>
       </c>
@@ -6691,7 +6691,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="85" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>242</v>
       </c>
@@ -7307,7 +7307,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>276</v>
       </c>
@@ -7351,7 +7351,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>279</v>
       </c>
@@ -9683,7 +9683,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>429</v>
       </c>
@@ -9859,7 +9859,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="157" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>437</v>
       </c>
@@ -10035,7 +10035,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>445</v>
       </c>
@@ -10079,7 +10079,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>447</v>
       </c>
@@ -10167,7 +10167,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>451</v>
       </c>
@@ -10871,7 +10871,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>485</v>
       </c>
@@ -11003,7 +11003,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>492</v>
       </c>
@@ -12059,7 +12059,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>553</v>
       </c>
@@ -12103,7 +12103,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>555</v>
       </c>
@@ -12895,7 +12895,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>599</v>
       </c>
@@ -15931,7 +15931,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>752</v>
       </c>
@@ -16679,7 +16679,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="312" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>797</v>
       </c>
@@ -16816,15 +16816,6 @@
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9824B75-038E-4818-8E8A-41D34C263D5F}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 

--- a/docs/Items.xlsx
+++ b/docs/Items.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\RE_Modding\BioRand\re7\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72A360A7-BD33-4A23-9CD3-3A847A46CEC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8006D013-8FF4-4C1E-A943-0F46613589FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38400" yWindow="2580" windowWidth="28800" windowHeight="15345" xr2:uid="{DE583D23-C62C-4A13-9B57-9882812AC707}"/>
+    <workbookView xWindow="38280" yWindow="2220" windowWidth="29040" windowHeight="15720" xr2:uid="{DE583D23-C62C-4A13-9B57-9882812AC707}"/>
   </bookViews>
   <sheets>
     <sheet name="items" sheetId="2" r:id="rId1"/>
@@ -2625,16 +2625,6 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8997F09E-7585-4546-A99D-93C95A83DDE6}" name="items" displayName="items" ref="A1:N314" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:N314" xr:uid="{8997F09E-7585-4546-A99D-93C95A83DDE6}">
-    <filterColumn colId="3">
-      <filters>
-        <filter val="Slot1"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="4">
-      <filters>
-        <filter val="WAHR"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="5">
       <filters blank="1"/>
     </filterColumn>
@@ -3039,7 +3029,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -3083,7 +3073,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -3171,7 +3161,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -3215,7 +3205,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -3259,7 +3249,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -3347,7 +3337,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -3435,7 +3425,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>46</v>
       </c>
@@ -3479,7 +3469,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>48</v>
       </c>
@@ -3523,7 +3513,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>51</v>
       </c>
@@ -3567,7 +3557,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>54</v>
       </c>
@@ -4095,7 +4085,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>89</v>
       </c>
@@ -4139,7 +4129,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="27" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>91</v>
       </c>
@@ -4183,7 +4173,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="28" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>94</v>
       </c>
@@ -4227,7 +4217,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="29" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>95</v>
       </c>
@@ -4271,7 +4261,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>97</v>
       </c>
@@ -4315,7 +4305,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="31" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>99</v>
       </c>
@@ -4359,7 +4349,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="32" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>101</v>
       </c>
@@ -4403,7 +4393,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="33" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>104</v>
       </c>
@@ -4447,7 +4437,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>105</v>
       </c>
@@ -4535,7 +4525,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>109</v>
       </c>
@@ -4579,7 +4569,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="37" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>111</v>
       </c>
@@ -4623,7 +4613,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="38" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>113</v>
       </c>
@@ -4667,7 +4657,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="39" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>115</v>
       </c>
@@ -4711,7 +4701,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="40" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>118</v>
       </c>
@@ -4755,7 +4745,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>121</v>
       </c>
@@ -4799,7 +4789,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="42" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>123</v>
       </c>
@@ -4843,7 +4833,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="43" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>125</v>
       </c>
@@ -4887,7 +4877,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>128</v>
       </c>
@@ -4931,7 +4921,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>131</v>
       </c>
@@ -4975,7 +4965,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>134</v>
       </c>
@@ -5019,7 +5009,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="47" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>137</v>
       </c>
@@ -5063,7 +5053,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="48" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>140</v>
       </c>
@@ -5151,7 +5141,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="50" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>145</v>
       </c>
@@ -5327,7 +5317,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>155</v>
       </c>
@@ -5459,7 +5449,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>165</v>
       </c>
@@ -5547,7 +5537,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>169</v>
       </c>
@@ -5635,7 +5625,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>174</v>
       </c>
@@ -6603,7 +6593,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>236</v>
       </c>
@@ -6647,7 +6637,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="84" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>239</v>
       </c>
@@ -6779,7 +6769,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="87" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>248</v>
       </c>
@@ -6867,7 +6857,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>252</v>
       </c>
@@ -6911,7 +6901,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="90" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>254</v>
       </c>
@@ -6955,7 +6945,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="91" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>257</v>
       </c>
@@ -6999,7 +6989,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="92" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>260</v>
       </c>
@@ -7043,7 +7033,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="93" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>262</v>
       </c>
@@ -7087,7 +7077,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="94" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>265</v>
       </c>
@@ -7131,7 +7121,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="95" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>267</v>
       </c>
@@ -7175,7 +7165,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="96" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>269</v>
       </c>
@@ -7219,7 +7209,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="97" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>271</v>
       </c>
@@ -7307,7 +7297,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>276</v>
       </c>
@@ -7351,7 +7341,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="100" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>279</v>
       </c>
@@ -7395,7 +7385,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="101" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>281</v>
       </c>
@@ -7439,7 +7429,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="102" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>284</v>
       </c>
@@ -8319,7 +8309,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="122" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>344</v>
       </c>
@@ -8363,7 +8353,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="123" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>346</v>
       </c>
@@ -8407,7 +8397,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="124" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>348</v>
       </c>
@@ -8451,7 +8441,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="125" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>350</v>
       </c>
@@ -8495,7 +8485,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="126" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>353</v>
       </c>
@@ -8539,7 +8529,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="127" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>354</v>
       </c>
@@ -9023,7 +9013,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="138" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>385</v>
       </c>
@@ -9067,7 +9057,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="139" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>388</v>
       </c>
@@ -9111,7 +9101,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="140" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>391</v>
       </c>
@@ -9639,7 +9629,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="152" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>427</v>
       </c>
@@ -9683,7 +9673,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="153" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>429</v>
       </c>
@@ -9727,7 +9717,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="154" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>431</v>
       </c>
@@ -9771,7 +9761,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="155" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>433</v>
       </c>
@@ -9815,7 +9805,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="156" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>435</v>
       </c>
@@ -9903,7 +9893,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="158" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>439</v>
       </c>
@@ -9947,7 +9937,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="159" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>441</v>
       </c>
@@ -9991,7 +9981,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="160" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>443</v>
       </c>
@@ -10035,7 +10025,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="161" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>445</v>
       </c>
@@ -10079,7 +10069,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="162" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>447</v>
       </c>
@@ -10167,7 +10157,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="164" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>451</v>
       </c>
@@ -10343,7 +10333,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="168" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>366</v>
       </c>
@@ -10387,7 +10377,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="169" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>459</v>
       </c>
@@ -10695,7 +10685,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="176" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>474</v>
       </c>
@@ -10739,7 +10729,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="177" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>477</v>
       </c>
@@ -10783,7 +10773,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="178" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>480</v>
       </c>
@@ -10827,7 +10817,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="179" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>483</v>
       </c>
@@ -10871,7 +10861,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="180" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>485</v>
       </c>
@@ -10915,7 +10905,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="181" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>487</v>
       </c>
@@ -10959,7 +10949,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="182" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>490</v>
       </c>
@@ -11003,7 +10993,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="183" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>492</v>
       </c>
@@ -11047,7 +11037,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="184" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>494</v>
       </c>
@@ -11091,7 +11081,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="185" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>117</v>
       </c>
@@ -11135,7 +11125,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="186" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>498</v>
       </c>
@@ -11179,7 +11169,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="187" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>501</v>
       </c>
@@ -11223,7 +11213,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="188" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>503</v>
       </c>
@@ -11399,7 +11389,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="192" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>513</v>
       </c>
@@ -11487,7 +11477,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="194" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>517</v>
       </c>
@@ -11531,7 +11521,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="195" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>520</v>
       </c>
@@ -11795,7 +11785,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="201" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>538</v>
       </c>
@@ -11839,7 +11829,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="202" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>541</v>
       </c>
@@ -11883,7 +11873,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="203" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>544</v>
       </c>
@@ -11927,7 +11917,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="204" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>547</v>
       </c>
@@ -11971,7 +11961,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="205" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>549</v>
       </c>
@@ -12059,7 +12049,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="207" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>553</v>
       </c>
@@ -12103,7 +12093,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="208" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>555</v>
       </c>
@@ -12191,7 +12181,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="210" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>559</v>
       </c>
@@ -12411,7 +12401,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="215" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>572</v>
       </c>
@@ -12455,7 +12445,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="216" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>575</v>
       </c>
@@ -12499,7 +12489,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="217" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>577</v>
       </c>
@@ -12543,7 +12533,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="218" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>579</v>
       </c>
@@ -12587,7 +12577,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="219" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>581</v>
       </c>
@@ -12631,7 +12621,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="220" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>583</v>
       </c>
@@ -12807,7 +12797,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="224" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>595</v>
       </c>
@@ -12851,7 +12841,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="225" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>597</v>
       </c>
@@ -12895,7 +12885,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="226" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>599</v>
       </c>
@@ -12939,7 +12929,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="227" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>601</v>
       </c>
@@ -12983,7 +12973,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="228" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>603</v>
       </c>
@@ -13027,7 +13017,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="229" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>606</v>
       </c>
@@ -13071,7 +13061,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="230" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>609</v>
       </c>
@@ -15183,7 +15173,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="278" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>705</v>
       </c>
@@ -15315,7 +15305,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="281" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>713</v>
       </c>
@@ -15931,7 +15921,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="295" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>752</v>
       </c>
@@ -15975,7 +15965,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="296" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>754</v>
       </c>
@@ -16019,7 +16009,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="297" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>757</v>
       </c>
@@ -16063,7 +16053,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="298" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>759</v>
       </c>
@@ -16107,7 +16097,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="299" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>762</v>
       </c>
@@ -16503,7 +16493,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="308" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>787</v>
       </c>
@@ -16547,7 +16537,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="309" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>790</v>
       </c>
@@ -16591,7 +16581,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="310" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>792</v>
       </c>
@@ -16723,7 +16713,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="313" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>799</v>
       </c>
@@ -16767,7 +16757,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="314" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>801</v>
       </c>

--- a/docs/Items.xlsx
+++ b/docs/Items.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\RE_Modding\BioRand\re7\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8006D013-8FF4-4C1E-A943-0F46613589FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA5C762-9BEA-4396-AF01-808ADFFE808D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="2220" windowWidth="29040" windowHeight="15720" xr2:uid="{DE583D23-C62C-4A13-9B57-9882812AC707}"/>
   </bookViews>
@@ -2625,6 +2625,12 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8997F09E-7585-4546-A99D-93C95A83DDE6}" name="items" displayName="items" ref="A1:N314" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:N314" xr:uid="{8997F09E-7585-4546-A99D-93C95A83DDE6}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="StackWeapon"/>
+        <filter val="Weapon"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="5">
       <filters blank="1"/>
     </filterColumn>
@@ -3029,7 +3035,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -3073,7 +3079,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -3161,7 +3167,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -3205,7 +3211,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -3249,7 +3255,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -3337,7 +3343,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -3381,7 +3387,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -3425,7 +3431,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>46</v>
       </c>
@@ -3469,7 +3475,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>48</v>
       </c>
@@ -3557,7 +3563,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>54</v>
       </c>
@@ -3997,7 +4003,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>83</v>
       </c>
@@ -4041,7 +4047,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>86</v>
       </c>
@@ -4085,7 +4091,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>89</v>
       </c>
@@ -4129,7 +4135,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>91</v>
       </c>
@@ -4217,7 +4223,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>95</v>
       </c>
@@ -4261,7 +4267,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>97</v>
       </c>
@@ -4305,7 +4311,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>99</v>
       </c>
@@ -4349,7 +4355,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>101</v>
       </c>
@@ -4525,7 +4531,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>109</v>
       </c>
@@ -4613,7 +4619,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>113</v>
       </c>
@@ -4657,7 +4663,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>115</v>
       </c>
@@ -4701,7 +4707,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>118</v>
       </c>
@@ -4745,7 +4751,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>121</v>
       </c>
@@ -4789,7 +4795,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>123</v>
       </c>
@@ -4833,7 +4839,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>125</v>
       </c>
@@ -4877,7 +4883,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>128</v>
       </c>
@@ -4921,7 +4927,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>131</v>
       </c>
@@ -4965,7 +4971,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>134</v>
       </c>
@@ -5009,7 +5015,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>137</v>
       </c>
@@ -5053,7 +5059,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>140</v>
       </c>
@@ -5317,7 +5323,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>155</v>
       </c>
@@ -5361,7 +5367,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>159</v>
       </c>
@@ -5449,7 +5455,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>165</v>
       </c>
@@ -5537,7 +5543,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>169</v>
       </c>
@@ -5625,7 +5631,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>174</v>
       </c>
@@ -6593,7 +6599,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>236</v>
       </c>
@@ -6637,7 +6643,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>239</v>
       </c>
@@ -6681,7 +6687,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>242</v>
       </c>
@@ -6769,7 +6775,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>248</v>
       </c>
@@ -6857,7 +6863,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>252</v>
       </c>
@@ -6901,7 +6907,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>254</v>
       </c>
@@ -6945,7 +6951,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>257</v>
       </c>
@@ -6989,7 +6995,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>260</v>
       </c>
@@ -7033,7 +7039,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>262</v>
       </c>
@@ -7077,7 +7083,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>265</v>
       </c>
@@ -7121,7 +7127,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>267</v>
       </c>
@@ -7165,7 +7171,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>269</v>
       </c>
@@ -7209,7 +7215,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>271</v>
       </c>
@@ -7297,7 +7303,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>276</v>
       </c>
@@ -7341,7 +7347,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>279</v>
       </c>
@@ -7385,7 +7391,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>281</v>
       </c>
@@ -7429,7 +7435,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>284</v>
       </c>
@@ -8309,7 +8315,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>344</v>
       </c>
@@ -8353,7 +8359,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>346</v>
       </c>
@@ -8397,7 +8403,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>348</v>
       </c>
@@ -8441,7 +8447,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>350</v>
       </c>
@@ -8485,7 +8491,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>353</v>
       </c>
@@ -8529,7 +8535,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>354</v>
       </c>
@@ -9013,7 +9019,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>385</v>
       </c>
@@ -9057,7 +9063,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>388</v>
       </c>
@@ -9101,7 +9107,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>391</v>
       </c>
@@ -9673,7 +9679,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>429</v>
       </c>
@@ -9761,7 +9767,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>433</v>
       </c>
@@ -10025,7 +10031,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>445</v>
       </c>
@@ -10069,7 +10075,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>447</v>
       </c>
@@ -10157,7 +10163,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>451</v>
       </c>
@@ -10377,7 +10383,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>459</v>
       </c>
@@ -10729,7 +10735,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>477</v>
       </c>
@@ -10773,7 +10779,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>480</v>
       </c>
@@ -10861,7 +10867,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>485</v>
       </c>
@@ -10905,7 +10911,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>487</v>
       </c>
@@ -10993,7 +10999,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>492</v>
       </c>
@@ -11037,7 +11043,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>494</v>
       </c>
@@ -11081,7 +11087,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>117</v>
       </c>
@@ -11125,7 +11131,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>498</v>
       </c>
@@ -11169,7 +11175,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>501</v>
       </c>
@@ -11389,7 +11395,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>513</v>
       </c>
@@ -11477,7 +11483,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>517</v>
       </c>
@@ -11521,7 +11527,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>520</v>
       </c>
@@ -11785,7 +11791,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>538</v>
       </c>
@@ -11829,7 +11835,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>541</v>
       </c>
@@ -11873,7 +11879,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>544</v>
       </c>
@@ -11917,7 +11923,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>547</v>
       </c>
@@ -11961,7 +11967,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>549</v>
       </c>
@@ -12049,7 +12055,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>553</v>
       </c>
@@ -12093,7 +12099,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>555</v>
       </c>
@@ -12181,7 +12187,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>559</v>
       </c>
@@ -12401,7 +12407,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>572</v>
       </c>
@@ -12445,7 +12451,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>575</v>
       </c>
@@ -12489,7 +12495,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>577</v>
       </c>
@@ -12533,7 +12539,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>579</v>
       </c>
@@ -12577,7 +12583,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>581</v>
       </c>
@@ -12621,7 +12627,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>583</v>
       </c>
@@ -12885,7 +12891,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>599</v>
       </c>
@@ -12929,7 +12935,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>601</v>
       </c>
@@ -12973,7 +12979,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>603</v>
       </c>
@@ -13017,7 +13023,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>606</v>
       </c>
@@ -13061,7 +13067,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>609</v>
       </c>
@@ -15173,7 +15179,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>705</v>
       </c>
@@ -15305,7 +15311,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>713</v>
       </c>
@@ -15921,7 +15927,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>752</v>
       </c>
@@ -15965,7 +15971,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>754</v>
       </c>
@@ -16009,7 +16015,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>757</v>
       </c>
@@ -16053,7 +16059,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>759</v>
       </c>
@@ -16097,7 +16103,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>762</v>
       </c>
@@ -16493,7 +16499,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>787</v>
       </c>
@@ -16537,7 +16543,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>790</v>
       </c>
@@ -16581,7 +16587,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>792</v>
       </c>
@@ -16669,7 +16675,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>797</v>
       </c>
@@ -16713,7 +16719,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>799</v>
       </c>
@@ -16757,7 +16763,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>801</v>
       </c>

--- a/docs/Items.xlsx
+++ b/docs/Items.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\RE_Modding\BioRand\re7\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AA5C762-9BEA-4396-AF01-808ADFFE808D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A29A7605-01F8-41DB-BFD0-F7A0F507BA3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="2220" windowWidth="29040" windowHeight="15720" xr2:uid="{DE583D23-C62C-4A13-9B57-9882812AC707}"/>
   </bookViews>
@@ -2625,12 +2625,6 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8997F09E-7585-4546-A99D-93C95A83DDE6}" name="items" displayName="items" ref="A1:N314" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:N314" xr:uid="{8997F09E-7585-4546-A99D-93C95A83DDE6}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="StackWeapon"/>
-        <filter val="Weapon"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="5">
       <filters blank="1"/>
     </filterColumn>
@@ -3035,7 +3029,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -3079,7 +3073,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -3167,7 +3161,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -3211,7 +3205,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -3255,7 +3249,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -3343,7 +3337,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -3387,7 +3381,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -3431,7 +3425,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>46</v>
       </c>
@@ -3475,7 +3469,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>48</v>
       </c>
@@ -3563,7 +3557,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>54</v>
       </c>
@@ -4003,7 +3997,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="24" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>83</v>
       </c>
@@ -4047,7 +4041,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>86</v>
       </c>
@@ -4091,7 +4085,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>89</v>
       </c>
@@ -4135,7 +4129,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="27" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>91</v>
       </c>
@@ -4223,7 +4217,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="29" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>95</v>
       </c>
@@ -4267,7 +4261,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>97</v>
       </c>
@@ -4311,7 +4305,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="31" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>99</v>
       </c>
@@ -4355,7 +4349,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="32" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>101</v>
       </c>
@@ -4531,7 +4525,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>109</v>
       </c>
@@ -4619,7 +4613,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="38" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>113</v>
       </c>
@@ -4663,7 +4657,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="39" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>115</v>
       </c>
@@ -4707,7 +4701,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="40" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>118</v>
       </c>
@@ -4751,7 +4745,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>121</v>
       </c>
@@ -4795,7 +4789,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="42" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>123</v>
       </c>
@@ -4839,7 +4833,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="43" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>125</v>
       </c>
@@ -4883,7 +4877,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>128</v>
       </c>
@@ -4927,7 +4921,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>131</v>
       </c>
@@ -4971,7 +4965,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>134</v>
       </c>
@@ -5015,7 +5009,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="47" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>137</v>
       </c>
@@ -5059,7 +5053,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="48" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>140</v>
       </c>
@@ -5323,7 +5317,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="54" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>155</v>
       </c>
@@ -5367,7 +5361,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>159</v>
       </c>
@@ -5455,7 +5449,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>165</v>
       </c>
@@ -5543,7 +5537,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="59" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>169</v>
       </c>
@@ -5631,7 +5625,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>174</v>
       </c>
@@ -6599,7 +6593,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="83" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>236</v>
       </c>
@@ -6643,7 +6637,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="84" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>239</v>
       </c>
@@ -6687,7 +6681,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="85" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>242</v>
       </c>
@@ -6775,7 +6769,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="87" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>248</v>
       </c>
@@ -6863,7 +6857,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="89" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>252</v>
       </c>
@@ -6907,7 +6901,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="90" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>254</v>
       </c>
@@ -6951,7 +6945,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="91" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>257</v>
       </c>
@@ -6995,7 +6989,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="92" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>260</v>
       </c>
@@ -7039,7 +7033,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="93" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>262</v>
       </c>
@@ -7083,7 +7077,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="94" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>265</v>
       </c>
@@ -7127,7 +7121,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="95" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>267</v>
       </c>
@@ -7171,7 +7165,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="96" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>269</v>
       </c>
@@ -7215,7 +7209,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="97" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>271</v>
       </c>
@@ -7303,7 +7297,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>276</v>
       </c>
@@ -7347,7 +7341,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="100" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>279</v>
       </c>
@@ -7391,7 +7385,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="101" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>281</v>
       </c>
@@ -7435,7 +7429,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="102" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>284</v>
       </c>
@@ -8315,7 +8309,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="122" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>344</v>
       </c>
@@ -8359,7 +8353,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="123" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>346</v>
       </c>
@@ -8403,7 +8397,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="124" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>348</v>
       </c>
@@ -8447,7 +8441,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="125" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>350</v>
       </c>
@@ -8491,7 +8485,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="126" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>353</v>
       </c>
@@ -8535,7 +8529,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="127" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>354</v>
       </c>
@@ -9019,7 +9013,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="138" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>385</v>
       </c>
@@ -9063,7 +9057,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="139" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>388</v>
       </c>
@@ -9107,7 +9101,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="140" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>391</v>
       </c>
@@ -9679,7 +9673,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="153" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>429</v>
       </c>
@@ -9767,7 +9761,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="155" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>433</v>
       </c>
@@ -10031,7 +10025,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="161" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>445</v>
       </c>
@@ -10075,7 +10069,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="162" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>447</v>
       </c>
@@ -10163,7 +10157,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="164" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>451</v>
       </c>
@@ -10383,7 +10377,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="169" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>459</v>
       </c>
@@ -10735,7 +10729,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="177" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>477</v>
       </c>
@@ -10779,7 +10773,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="178" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>480</v>
       </c>
@@ -10867,7 +10861,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="180" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>485</v>
       </c>
@@ -10911,7 +10905,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="181" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>487</v>
       </c>
@@ -10999,7 +10993,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="183" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>492</v>
       </c>
@@ -11043,7 +11037,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="184" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>494</v>
       </c>
@@ -11087,7 +11081,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="185" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>117</v>
       </c>
@@ -11131,7 +11125,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="186" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>498</v>
       </c>
@@ -11175,7 +11169,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="187" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>501</v>
       </c>
@@ -11395,7 +11389,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="192" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>513</v>
       </c>
@@ -11483,7 +11477,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="194" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>517</v>
       </c>
@@ -11527,7 +11521,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="195" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>520</v>
       </c>
@@ -11791,7 +11785,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="201" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>538</v>
       </c>
@@ -11835,7 +11829,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="202" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>541</v>
       </c>
@@ -11879,7 +11873,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="203" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>544</v>
       </c>
@@ -11923,7 +11917,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="204" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>547</v>
       </c>
@@ -11967,7 +11961,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="205" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>549</v>
       </c>
@@ -12055,7 +12049,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="207" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>553</v>
       </c>
@@ -12099,7 +12093,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="208" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>555</v>
       </c>
@@ -12187,7 +12181,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="210" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>559</v>
       </c>
@@ -12407,7 +12401,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="215" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>572</v>
       </c>
@@ -12451,7 +12445,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="216" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>575</v>
       </c>
@@ -12495,7 +12489,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="217" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>577</v>
       </c>
@@ -12539,7 +12533,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="218" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>579</v>
       </c>
@@ -12583,7 +12577,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="219" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>581</v>
       </c>
@@ -12627,7 +12621,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="220" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>583</v>
       </c>
@@ -12891,7 +12885,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="226" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>599</v>
       </c>
@@ -12935,7 +12929,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="227" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>601</v>
       </c>
@@ -12979,7 +12973,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="228" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>603</v>
       </c>
@@ -13023,7 +13017,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="229" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>606</v>
       </c>
@@ -13067,7 +13061,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="230" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>609</v>
       </c>
@@ -15179,7 +15173,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="278" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>705</v>
       </c>
@@ -15311,7 +15305,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="281" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>713</v>
       </c>
@@ -15927,7 +15921,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="295" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>752</v>
       </c>
@@ -15971,7 +15965,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="296" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>754</v>
       </c>
@@ -16015,7 +16009,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="297" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>757</v>
       </c>
@@ -16059,7 +16053,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="298" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>759</v>
       </c>
@@ -16103,7 +16097,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="299" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>762</v>
       </c>
@@ -16499,7 +16493,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="308" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>787</v>
       </c>
@@ -16543,7 +16537,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="309" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>790</v>
       </c>
@@ -16587,7 +16581,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="310" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>792</v>
       </c>
@@ -16675,7 +16669,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="312" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>797</v>
       </c>
@@ -16719,7 +16713,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="313" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>799</v>
       </c>
@@ -16763,7 +16757,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="314" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>801</v>
       </c>

--- a/docs/Items.xlsx
+++ b/docs/Items.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\RE_Modding\BioRand\re7\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A29A7605-01F8-41DB-BFD0-F7A0F507BA3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32BA5522-0AB6-4704-AD28-C73EEC8F74DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="2220" windowWidth="29040" windowHeight="15720" xr2:uid="{DE583D23-C62C-4A13-9B57-9882812AC707}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{DE583D23-C62C-4A13-9B57-9882812AC707}"/>
   </bookViews>
   <sheets>
     <sheet name="items" sheetId="2" r:id="rId1"/>
@@ -2624,11 +2624,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8997F09E-7585-4546-A99D-93C95A83DDE6}" name="items" displayName="items" ref="A1:N314" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:N314" xr:uid="{8997F09E-7585-4546-A99D-93C95A83DDE6}">
-    <filterColumn colId="5">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:N314" xr:uid="{8997F09E-7585-4546-A99D-93C95A83DDE6}"/>
   <tableColumns count="14">
     <tableColumn id="1" xr3:uid="{F0F4938D-6AE6-4FD1-903A-6D70073C8CFE}" uniqueName="1" name="Id" queryTableFieldId="1" dataDxfId="12"/>
     <tableColumn id="2" xr3:uid="{0EDD0777-3DC7-4A87-90CA-8CAF0D26BB97}" uniqueName="2" name="Name" queryTableFieldId="2" dataDxfId="11"/>
@@ -3117,7 +3113,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -3293,7 +3289,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>37</v>
       </c>
@@ -3601,7 +3597,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>55</v>
       </c>
@@ -3645,7 +3641,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>60</v>
       </c>
@@ -3689,7 +3685,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>63</v>
       </c>
@@ -3733,7 +3729,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>66</v>
       </c>
@@ -3777,7 +3773,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>69</v>
       </c>
@@ -3821,7 +3817,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>72</v>
       </c>
@@ -3865,7 +3861,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>74</v>
       </c>
@@ -3909,7 +3905,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>77</v>
       </c>
@@ -3953,7 +3949,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>80</v>
       </c>
@@ -4481,7 +4477,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="35" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>106</v>
       </c>
@@ -5185,7 +5181,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>146</v>
       </c>
@@ -5229,7 +5225,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="52" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>149</v>
       </c>
@@ -5273,7 +5269,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="53" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>152</v>
       </c>
@@ -5405,7 +5401,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>162</v>
       </c>
@@ -5493,7 +5489,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>167</v>
       </c>
@@ -5581,7 +5577,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="60" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>171</v>
       </c>
@@ -5669,7 +5665,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="62" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>177</v>
       </c>
@@ -5713,7 +5709,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="63" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>179</v>
       </c>
@@ -5757,7 +5753,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="64" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>182</v>
       </c>
@@ -5801,7 +5797,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>184</v>
       </c>
@@ -5845,7 +5841,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="66" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>186</v>
       </c>
@@ -5889,7 +5885,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="67" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>189</v>
       </c>
@@ -5933,7 +5929,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="68" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>192</v>
       </c>
@@ -5977,7 +5973,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="69" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>194</v>
       </c>
@@ -6021,7 +6017,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="70" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>196</v>
       </c>
@@ -6065,7 +6061,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>200</v>
       </c>
@@ -6109,7 +6105,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="72" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>203</v>
       </c>
@@ -6153,7 +6149,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>206</v>
       </c>
@@ -6197,7 +6193,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="74" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>209</v>
       </c>
@@ -6241,7 +6237,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>212</v>
       </c>
@@ -6285,7 +6281,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>215</v>
       </c>
@@ -6329,7 +6325,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="77" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>218</v>
       </c>
@@ -6373,7 +6369,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>221</v>
       </c>
@@ -6417,7 +6413,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="79" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>224</v>
       </c>
@@ -6461,7 +6457,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="80" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>227</v>
       </c>
@@ -6505,7 +6501,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>230</v>
       </c>
@@ -6549,7 +6545,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="82" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>233</v>
       </c>
@@ -6725,7 +6721,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="86" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>245</v>
       </c>
@@ -6813,7 +6809,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="88" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>250</v>
       </c>
@@ -7253,7 +7249,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="98" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>274</v>
       </c>
@@ -7473,7 +7469,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="103" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>287</v>
       </c>
@@ -7517,7 +7513,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="104" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>290</v>
       </c>
@@ -7561,7 +7557,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="105" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>293</v>
       </c>
@@ -7605,7 +7601,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="106" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>296</v>
       </c>
@@ -7649,7 +7645,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="107" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>299</v>
       </c>
@@ -7693,7 +7689,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="108" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>302</v>
       </c>
@@ -7737,7 +7733,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="109" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>305</v>
       </c>
@@ -7781,7 +7777,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="110" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>308</v>
       </c>
@@ -7825,7 +7821,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="111" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>311</v>
       </c>
@@ -7869,7 +7865,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="112" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>314</v>
       </c>
@@ -7913,7 +7909,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="113" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>317</v>
       </c>
@@ -7957,7 +7953,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="114" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>320</v>
       </c>
@@ -8001,7 +7997,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="115" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>323</v>
       </c>
@@ -8045,7 +8041,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="116" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>326</v>
       </c>
@@ -8089,7 +8085,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="117" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>329</v>
       </c>
@@ -8133,7 +8129,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="118" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>332</v>
       </c>
@@ -8177,7 +8173,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="119" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>335</v>
       </c>
@@ -8221,7 +8217,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="120" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>338</v>
       </c>
@@ -8265,7 +8261,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="121" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>341</v>
       </c>
@@ -8573,7 +8569,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="128" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>357</v>
       </c>
@@ -8617,7 +8613,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="129" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>360</v>
       </c>
@@ -8661,7 +8657,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="130" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>363</v>
       </c>
@@ -8705,7 +8701,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="131" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>365</v>
       </c>
@@ -8749,7 +8745,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="132" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>367</v>
       </c>
@@ -8793,7 +8789,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="133" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>370</v>
       </c>
@@ -8837,7 +8833,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="134" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>373</v>
       </c>
@@ -8881,7 +8877,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="135" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>376</v>
       </c>
@@ -8925,7 +8921,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="136" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>379</v>
       </c>
@@ -8969,7 +8965,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="137" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>382</v>
       </c>
@@ -9145,7 +9141,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="141" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>392</v>
       </c>
@@ -9189,7 +9185,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="142" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>395</v>
       </c>
@@ -9233,7 +9229,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="143" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>398</v>
       </c>
@@ -9277,7 +9273,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="144" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>401</v>
       </c>
@@ -9321,7 +9317,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="145" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>403</v>
       </c>
@@ -9365,7 +9361,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="146" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>404</v>
       </c>
@@ -9409,7 +9405,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="147" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>408</v>
       </c>
@@ -9453,7 +9449,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="148" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>412</v>
       </c>
@@ -9497,7 +9493,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="149" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>416</v>
       </c>
@@ -9541,7 +9537,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="150" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>420</v>
       </c>
@@ -9585,7 +9581,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="151" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>424</v>
       </c>
@@ -10113,7 +10109,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="163" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>449</v>
       </c>
@@ -10201,7 +10197,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="165" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>453</v>
       </c>
@@ -10245,7 +10241,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="166" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>455</v>
       </c>
@@ -10289,7 +10285,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="167" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>456</v>
       </c>
@@ -10421,7 +10417,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="170" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>461</v>
       </c>
@@ -10465,7 +10461,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="171" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>462</v>
       </c>
@@ -10509,7 +10505,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="172" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>465</v>
       </c>
@@ -10553,7 +10549,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="173" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>468</v>
       </c>
@@ -10597,7 +10593,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="174" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>471</v>
       </c>
@@ -10641,7 +10637,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="175" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>472</v>
       </c>
@@ -11257,7 +11253,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="189" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>505</v>
       </c>
@@ -11301,7 +11297,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="190" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>507</v>
       </c>
@@ -11345,7 +11341,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="191" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>510</v>
       </c>
@@ -11433,7 +11429,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="193" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>515</v>
       </c>
@@ -11565,7 +11561,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="196" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>523</v>
       </c>
@@ -11609,7 +11605,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="197" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>526</v>
       </c>
@@ -11653,7 +11649,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="198" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>529</v>
       </c>
@@ -11697,7 +11693,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="199" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>532</v>
       </c>
@@ -11741,7 +11737,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="200" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>535</v>
       </c>
@@ -12005,7 +12001,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="206" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>551</v>
       </c>
@@ -12137,7 +12133,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="209" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>557</v>
       </c>
@@ -12225,7 +12221,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="211" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>562</v>
       </c>
@@ -12269,7 +12265,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="212" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>565</v>
       </c>
@@ -12313,7 +12309,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="213" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>567</v>
       </c>
@@ -12357,7 +12353,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="214" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>569</v>
       </c>
@@ -12665,7 +12661,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="221" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>586</v>
       </c>
@@ -12709,7 +12705,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="222" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>589</v>
       </c>
@@ -12753,7 +12749,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="223" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>592</v>
       </c>
@@ -13105,7 +13101,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="231" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>611</v>
       </c>
@@ -13149,7 +13145,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="232" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>614</v>
       </c>
@@ -13193,7 +13189,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="233" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>615</v>
       </c>
@@ -13237,7 +13233,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="234" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>618</v>
       </c>
@@ -13281,7 +13277,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="235" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>619</v>
       </c>
@@ -13325,7 +13321,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="236" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>622</v>
       </c>
@@ -13369,7 +13365,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="237" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>623</v>
       </c>
@@ -13413,7 +13409,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="238" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>626</v>
       </c>
@@ -13457,7 +13453,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="239" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>627</v>
       </c>
@@ -13501,7 +13497,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="240" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>630</v>
       </c>
@@ -13545,7 +13541,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="241" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>631</v>
       </c>
@@ -13589,7 +13585,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="242" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>634</v>
       </c>
@@ -13633,7 +13629,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="243" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>635</v>
       </c>
@@ -13677,7 +13673,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="244" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>638</v>
       </c>
@@ -13721,7 +13717,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="245" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>639</v>
       </c>
@@ -13765,7 +13761,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="246" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>642</v>
       </c>
@@ -13809,7 +13805,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="247" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>643</v>
       </c>
@@ -13853,7 +13849,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="248" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>646</v>
       </c>
@@ -13897,7 +13893,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="249" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>647</v>
       </c>
@@ -13941,7 +13937,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="250" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>650</v>
       </c>
@@ -13985,7 +13981,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="251" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>651</v>
       </c>
@@ -14029,7 +14025,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="252" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>654</v>
       </c>
@@ -14073,7 +14069,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="253" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>655</v>
       </c>
@@ -14117,7 +14113,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="254" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>658</v>
       </c>
@@ -14161,7 +14157,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="255" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>659</v>
       </c>
@@ -14205,7 +14201,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="256" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>662</v>
       </c>
@@ -14249,7 +14245,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="257" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>663</v>
       </c>
@@ -14293,7 +14289,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="258" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>666</v>
       </c>
@@ -14337,7 +14333,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="259" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>667</v>
       </c>
@@ -14381,7 +14377,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="260" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>670</v>
       </c>
@@ -14425,7 +14421,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="261" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>671</v>
       </c>
@@ -14469,7 +14465,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="262" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>674</v>
       </c>
@@ -14513,7 +14509,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="263" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>675</v>
       </c>
@@ -14557,7 +14553,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="264" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>678</v>
       </c>
@@ -14601,7 +14597,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="265" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>679</v>
       </c>
@@ -14645,7 +14641,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="266" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>682</v>
       </c>
@@ -14689,7 +14685,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="267" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>683</v>
       </c>
@@ -14733,7 +14729,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="268" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>686</v>
       </c>
@@ -14777,7 +14773,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="269" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>687</v>
       </c>
@@ -14821,7 +14817,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="270" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>690</v>
       </c>
@@ -14865,7 +14861,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="271" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>691</v>
       </c>
@@ -14909,7 +14905,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="272" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>694</v>
       </c>
@@ -14953,7 +14949,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="273" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>695</v>
       </c>
@@ -14997,7 +14993,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="274" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>698</v>
       </c>
@@ -15041,7 +15037,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="275" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>699</v>
       </c>
@@ -15085,7 +15081,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="276" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>702</v>
       </c>
@@ -15129,7 +15125,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="277" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>703</v>
       </c>
@@ -15217,7 +15213,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="279" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>707</v>
       </c>
@@ -15261,7 +15257,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="280" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>710</v>
       </c>
@@ -15349,7 +15345,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="282" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>715</v>
       </c>
@@ -15393,7 +15389,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="283" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>717</v>
       </c>
@@ -15437,7 +15433,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="284" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>720</v>
       </c>
@@ -15481,7 +15477,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="285" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>723</v>
       </c>
@@ -15525,7 +15521,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="286" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>726</v>
       </c>
@@ -15569,7 +15565,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="287" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>729</v>
       </c>
@@ -15613,7 +15609,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="288" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>732</v>
       </c>
@@ -15657,7 +15653,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="289" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>735</v>
       </c>
@@ -15701,7 +15697,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="290" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>738</v>
       </c>
@@ -15745,7 +15741,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="291" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>741</v>
       </c>
@@ -15789,7 +15785,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="292" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>744</v>
       </c>
@@ -15833,7 +15829,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="293" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>746</v>
       </c>
@@ -15877,7 +15873,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="294" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>749</v>
       </c>
@@ -16141,7 +16137,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="300" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>764</v>
       </c>
@@ -16185,7 +16181,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="301" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>766</v>
       </c>
@@ -16229,7 +16225,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="302" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>769</v>
       </c>
@@ -16273,7 +16269,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="303" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>772</v>
       </c>
@@ -16317,7 +16313,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="304" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>775</v>
       </c>
@@ -16361,7 +16357,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="305" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>778</v>
       </c>
@@ -16405,7 +16401,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="306" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>781</v>
       </c>
@@ -16449,7 +16445,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="307" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>784</v>
       </c>
@@ -16625,7 +16621,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="311" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>794</v>
       </c>
